--- a/ig/test-tabs-svs/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/test-tabs-svs/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="2559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2643" uniqueCount="2641">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260601120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -714,7 +714,7 @@
     <t>0182</t>
   </si>
   <si>
-    <t>Education thérapeutique labellisée du patient asthmatique (école de l'asthme)</t>
+    <t>Programme d’ETP labellisée - Asthme</t>
   </si>
   <si>
     <t>0183</t>
@@ -1842,7 +1842,7 @@
     <t>0538</t>
   </si>
   <si>
-    <t>Thérapie de groupe ou atelier à médiation orale et/ou écrite (groupe de parole, d'écriture)</t>
+    <t>Thérapie de groupe ou atelier à médiation orale et-ou écrite (groupe de parole, d'écriture)</t>
   </si>
   <si>
     <t>0539</t>
@@ -4134,7 +4134,7 @@
     <t>1014</t>
   </si>
   <si>
-    <t>Fourniture de matériel d’hygiène, de prévention et de Réduction des Risques et des Dommages (RdRD)</t>
+    <t>Fourniture de matériel d'hygiène, de prévention et de RdRD</t>
   </si>
   <si>
     <t>1015</t>
@@ -5694,13 +5694,13 @@
     <t>1281</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Affections neurologiques</t>
+    <t>Programme d'ETP labellisée - Affections neurologiques (hors AVC)</t>
   </si>
   <si>
     <t>1282</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Diabète et pathologies endocrines</t>
+    <t>Programme d'ETP labellisée - Diabète</t>
   </si>
   <si>
     <t>1283</t>
@@ -5724,7 +5724,7 @@
     <t>1286</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Maladies Cancéreuses</t>
+    <t>Programme d'ETP labellisée - Maladies Cancéreuses (dont soins de support)</t>
   </si>
   <si>
     <t>1287</t>
@@ -5742,13 +5742,13 @@
     <t>1289</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Maladies du système ostéoarticulaire</t>
+    <t>Programme d'ETP labellisée - Maladies rhumatologiques et du système ostéoarticulaire</t>
   </si>
   <si>
     <t>1290</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Maladies infectieuses</t>
+    <t>Programme d'ETP labellisée - Maladies infectieuses chroniques (dont VIH et tuberculose)</t>
   </si>
   <si>
     <t>1291</t>
@@ -6594,7 +6594,7 @@
     <t>1447</t>
   </si>
   <si>
-    <t>Prescription de vaccination</t>
+    <t>Prescription de vaccin</t>
   </si>
   <si>
     <t>1448</t>
@@ -6624,7 +6624,7 @@
     <t>1453</t>
   </si>
   <si>
-    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
+    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
   </si>
   <si>
     <t>1454</t>
@@ -7362,7 +7362,7 @@
     <t>1578</t>
   </si>
   <si>
-    <t>Centre expert Parkinson</t>
+    <t>Centre expert en maladie de Parkinson</t>
   </si>
   <si>
     <t>1579</t>
@@ -7386,301 +7386,547 @@
     <t>1582</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en cardiologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en cardiologie</t>
   </si>
   <si>
     <t>1583</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie cardiaque et gros vaisseaux</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie cardiaque et gros vaisseaux</t>
   </si>
   <si>
     <t>1584</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie digestive et viscérale</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie digestive et viscérale</t>
   </si>
   <si>
     <t>1585</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie maxillo-faciale et stomatologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie maxillo-faciale et stomatologie</t>
   </si>
   <si>
     <t>1586</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie orthopédique et traumatologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie orthopédique et traumatologie</t>
   </si>
   <si>
     <t>1587</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie pédiatrique orthopédique et traumatologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique orthopédique et traumatologie</t>
   </si>
   <si>
     <t>1588</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie pédiatrique viscérale et digestive</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique viscérale et digestive</t>
   </si>
   <si>
     <t>1589</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie thoracique et pulmonaire</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie thoracique et pulmonaire</t>
   </si>
   <si>
     <t>1590</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie vasculaire</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie vasculaire</t>
   </si>
   <si>
     <t>1591</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en dermatologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en dermatologie</t>
   </si>
   <si>
     <t>1592</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en endocrinologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en endocrinologie</t>
   </si>
   <si>
     <t>1593</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en gériatrie (gérontologie)</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gériatrie (gérontologie)</t>
   </si>
   <si>
     <t>1594</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en gynécologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gynécologie</t>
   </si>
   <si>
     <t>1595</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en hématologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hématologie</t>
   </si>
   <si>
     <t>1596</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en hépato-gastro-entérologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hépato-gastro-entérologie</t>
   </si>
   <si>
     <t>1597</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en maladies infectieuses et tropicales</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en maladies infectieuses et tropicales</t>
   </si>
   <si>
     <t>1598</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en médecine interne</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine interne</t>
   </si>
   <si>
     <t>1599</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en médecine vasculaire</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine vasculaire</t>
   </si>
   <si>
     <t>1600</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en néphrologie (dont dialyse)</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en néphrologie (dont dialyse)</t>
   </si>
   <si>
     <t>1601</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en neurochirurgie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurochirurgie</t>
   </si>
   <si>
     <t>1602</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en neurologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurologie</t>
   </si>
   <si>
     <t>1603</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en oncologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oncologie</t>
   </si>
   <si>
     <t>1604</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en ophtalmologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en ophtalmologie</t>
   </si>
   <si>
     <t>1605</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
   </si>
   <si>
     <t>1606</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en pédiatrie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pédiatrie</t>
   </si>
   <si>
     <t>1607</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en pneumologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pneumologie</t>
   </si>
   <si>
     <t>1608</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en rhumatologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en rhumatologie</t>
   </si>
   <si>
     <t>1609</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en urologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en urologie</t>
   </si>
   <si>
     <t>1610</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en caisson oxygène hyperbare</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en caisson oxygène hyperbare</t>
   </si>
   <si>
     <t>1611</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie de la main SOS main</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie de la main SOS main</t>
   </si>
   <si>
     <t>1612</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en odontologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en odontologie</t>
   </si>
   <si>
     <t>1613</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en psychiatrie (dont équipe de liaison)</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en psychiatrie (dont équipe de liaison)</t>
   </si>
   <si>
     <t>1614</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en radiologie interventionnelle</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en radiologie interventionnelle</t>
   </si>
   <si>
     <t>1615</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue rachis</t>
-  </si>
-  <si>
-    <t>1616</t>
-  </si>
-  <si>
-    <t>Pédicurie-podologie conventionnée du pied diabétique de grade 2 et 3</t>
-  </si>
-  <si>
-    <t>1617</t>
-  </si>
-  <si>
-    <t>Pédicurie-podologie conventionnée soins de support oncologie</t>
-  </si>
-  <si>
-    <t>1618</t>
-  </si>
-  <si>
-    <t>Orthoplastie (appareillage d’orteil)</t>
-  </si>
-  <si>
-    <t>1619</t>
-  </si>
-  <si>
-    <t>Orthonyxie (appareillage d’ongle)</t>
-  </si>
-  <si>
-    <t>1620</t>
-  </si>
-  <si>
-    <t>Onychoplastie (reconstruction de l’ongle)</t>
-  </si>
-  <si>
-    <t>1621</t>
-  </si>
-  <si>
-    <t>Orthèse plantaire (semelle orthopédique)</t>
-  </si>
-  <si>
-    <t>1622</t>
-  </si>
-  <si>
-    <t>Bilan diagnostique podologique de la prévention de la chute</t>
-  </si>
-  <si>
-    <t>1623</t>
-  </si>
-  <si>
-    <t>Rééducation du pied (sous la cheville)</t>
-  </si>
-  <si>
-    <t>1624</t>
-  </si>
-  <si>
-    <t>Contention nocturne</t>
-  </si>
-  <si>
-    <t>1625</t>
-  </si>
-  <si>
-    <t>Soin de pédicurie</t>
-  </si>
-  <si>
-    <t>1626</t>
-  </si>
-  <si>
-    <t>Traitement de la verrue plantaire par azote liquide</t>
-  </si>
-  <si>
-    <t>1627</t>
-  </si>
-  <si>
-    <t>Traitement sans douleur de l’ongle incarné par phénolisation (protocole de coopération)</t>
-  </si>
-  <si>
-    <t>1628</t>
-  </si>
-  <si>
-    <t>Prélèvement unguéal pour analyse biologique (protocole de coopération)</t>
-  </si>
-  <si>
-    <t>1629</t>
-  </si>
-  <si>
-    <t>Confection de semelle de comblement en polyuréthane (PU) pour amputation partielle du pied</t>
-  </si>
-  <si>
-    <t>1630</t>
-  </si>
-  <si>
-    <t>Prise en charge spécialisée et continue en pédopsychiatrie (dont équipe de liaison)</t>
-  </si>
-  <si>
-    <t>1631</t>
-  </si>
-  <si>
-    <t>Prise en charge spécialisée et continue SOS main</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) rachis</t>
+  </si>
+  <si>
+    <t>1632</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Accident Vasculaire Cérébral (AVC)</t>
+  </si>
+  <si>
+    <t>1633</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Allergologie</t>
+  </si>
+  <si>
+    <t>1634</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Anticoagulants oraux (AVK, AOD, HBPM)</t>
+  </si>
+  <si>
+    <t>1635</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Maladies rares (dont maladies du sang, drépanocytose, amylose)</t>
+  </si>
+  <si>
+    <t>1636</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Maladies urologiques et gynécologiques</t>
+  </si>
+  <si>
+    <t>1637</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Obésité</t>
+  </si>
+  <si>
+    <t>1638</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Ophtalmologie</t>
+  </si>
+  <si>
+    <t>1639</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Pathologies endocrines (hors diabète, hors obésité)</t>
+  </si>
+  <si>
+    <t>1640</t>
+  </si>
+  <si>
+    <t>Lyophilisation de lait maternel</t>
+  </si>
+  <si>
+    <t>1641</t>
+  </si>
+  <si>
+    <t>Centre de Traitement des Brûlés (CTB)</t>
+  </si>
+  <si>
+    <t>1642</t>
+  </si>
+  <si>
+    <t>Remédiation psychosociale</t>
+  </si>
+  <si>
+    <t>1643</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice d’un trouble du neurodéveloppement</t>
+  </si>
+  <si>
+    <t>1644</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice d’un trouble de l’apprentissage</t>
+  </si>
+  <si>
+    <t>1645</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice des troubles tonico-émotionnels</t>
+  </si>
+  <si>
+    <t>1646</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice des troubles de la latéralisation</t>
+  </si>
+  <si>
+    <t>1647</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice du schéma corporel et des représentations du corps</t>
+  </si>
+  <si>
+    <t>1648</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice des troubles d’organisation spatio-temporelle</t>
+  </si>
+  <si>
+    <t>1649</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice des troubles sensoriels</t>
+  </si>
+  <si>
+    <t>1650</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice du développement psychomoteur</t>
+  </si>
+  <si>
+    <t>1651</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice des troubles psychiques</t>
+  </si>
+  <si>
+    <t>1652</t>
+  </si>
+  <si>
+    <t>Programmes d’Entraînement aux Habiletés Parentales</t>
+  </si>
+  <si>
+    <t>1653</t>
+  </si>
+  <si>
+    <t>Relaxation psychomotrice</t>
+  </si>
+  <si>
+    <t>1654</t>
+  </si>
+  <si>
+    <t>Evaluation et/ou prise en soins orthoptiques à visée visio-vestibulaire dans le cadre des troubles de l'équilibration et vertiges</t>
+  </si>
+  <si>
+    <t>1655</t>
+  </si>
+  <si>
+    <t>Evaluation visuelle des troubles orthoptiques et neurovisuels dans le cadre des troubles du neuro-développement (TNV - TND)</t>
+  </si>
+  <si>
+    <t>1656</t>
+  </si>
+  <si>
+    <t>Bilan de dépistage réfractif et de l'amblyopie</t>
+  </si>
+  <si>
+    <t>1657</t>
+  </si>
+  <si>
+    <t>Bilan visuel dans le cadre d'un renouvellement ou d'une adaptation de la correction optique (Protocole de coopération Renouvellement d'Optique (RNO))</t>
+  </si>
+  <si>
+    <t>1658</t>
+  </si>
+  <si>
+    <t>Exploration du sens chromatique</t>
+  </si>
+  <si>
+    <t>1659</t>
+  </si>
+  <si>
+    <t>Examen de la courbe d'adaptation à l'obscurité</t>
+  </si>
+  <si>
+    <t>1660</t>
+  </si>
+  <si>
+    <t>Protocole de dépistage de la rétinopathie diabétique</t>
+  </si>
+  <si>
+    <t>1661</t>
+  </si>
+  <si>
+    <t>Examen dépistage réfractif avec Photoscreener</t>
+  </si>
+  <si>
+    <t>1662</t>
+  </si>
+  <si>
+    <t>Bilan visuel primo-prescription ou renouvellement de la correction optique (lunettes, lentilles, souples) pour les patients de 16 ans à 42 ans</t>
+  </si>
+  <si>
+    <t>1663</t>
+  </si>
+  <si>
+    <t>Evaluation oculométrique par enregistrement – technique d'Eye tracking</t>
+  </si>
+  <si>
+    <t>1664</t>
+  </si>
+  <si>
+    <t>Evaluation et/ou prise en soins dans le cadre de particularités sensorielles et perceptives (profil sensoriel de DUNN, BOGDASHINA)</t>
+  </si>
+  <si>
+    <t>1665</t>
+  </si>
+  <si>
+    <t>Evaluation orthoptique et/ou prise en soins avec ajustement d'aide optique et nouvelle technologie associé à un handicap de la fonction visuelle (RV)</t>
+  </si>
+  <si>
+    <t>1666</t>
+  </si>
+  <si>
+    <t>Evaluation et suivi dans le cadre de l'adaptation du logement lors d'un handicap de la fonction visuelle</t>
+  </si>
+  <si>
+    <t>1667</t>
+  </si>
+  <si>
+    <t>Evaluation orthoptique de la fonction visuelle et/ou prise en soins dans le cadre de la conduite automobile</t>
+  </si>
+  <si>
+    <t>1668</t>
+  </si>
+  <si>
+    <t>Evaluation orthoptique de la fonction visuelle et/ou prise en soins dans le cadre de l'activité physique adaptée</t>
+  </si>
+  <si>
+    <t>1669</t>
+  </si>
+  <si>
+    <t>Evaluation et/ou prise en soins orthoptiques neurovisuels des troubles de la cognition visuelle</t>
+  </si>
+  <si>
+    <t>1670</t>
+  </si>
+  <si>
+    <t>Evaluation et/ou prise en soins de la rééducation neurovisuelle visuo-vestibulaire (vertiges)</t>
+  </si>
+  <si>
+    <t>1671</t>
+  </si>
+  <si>
+    <t>Dispensation médicamenteuse à domicile en cas d’impossibilité du patient à se déplacer</t>
+  </si>
+  <si>
+    <t>1672</t>
+  </si>
+  <si>
+    <t>Préparation des doses à administrer (PDA)</t>
+  </si>
+  <si>
+    <t>1673</t>
+  </si>
+  <si>
+    <t>Entretien pharmaceutique de la femme enceinte</t>
+  </si>
+  <si>
+    <t>1674</t>
+  </si>
+  <si>
+    <t>Entretien pharmaceutique du patient asthmatique sous corticostéroïdes inhalés (CSI)</t>
+  </si>
+  <si>
+    <t>1675</t>
+  </si>
+  <si>
+    <t>Entretien pharmaceutique du patient sous anticoagulant oral (AOD/AVK)</t>
+  </si>
+  <si>
+    <t>1676</t>
+  </si>
+  <si>
+    <t>Entretien pharmaceutique du patient sous anticancéreux oraux</t>
+  </si>
+  <si>
+    <t>1677</t>
+  </si>
+  <si>
+    <t>Entretien pharmaceutique du patient sous antalgique opioïde de pallier 2</t>
+  </si>
+  <si>
+    <t>1678</t>
+  </si>
+  <si>
+    <t>Entretien bilan partagé de médication</t>
+  </si>
+  <si>
+    <t>1679</t>
+  </si>
+  <si>
+    <t>Réseau France Santé</t>
+  </si>
+  <si>
+    <t>1680</t>
+  </si>
+  <si>
+    <t>Autorisation par l’ARS pour la sous-traitance de préparation pharmaceutique</t>
+  </si>
+  <si>
+    <t>1681</t>
+  </si>
+  <si>
+    <t>Orthèses et prothèses externes (orthopédie sur mesure)</t>
+  </si>
+  <si>
+    <t>1682</t>
+  </si>
+  <si>
+    <t>Orthèses et prothèses externes (de série)</t>
+  </si>
+  <si>
+    <t>1683</t>
+  </si>
+  <si>
+    <t>Optique lunetterie</t>
+  </si>
+  <si>
+    <t>1684</t>
+  </si>
+  <si>
+    <t>Audioprothèse</t>
+  </si>
+  <si>
+    <t>1685</t>
+  </si>
+  <si>
+    <t>Prise en charge de l’éruption cutanée vésiculeuse prurigineuse chez l’enfant (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1686</t>
+  </si>
+  <si>
+    <t>Renouvellement du traitement de la rhino-conjonctivite allergique saisonnière (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1687</t>
+  </si>
+  <si>
+    <t>Distribution de comprimés d’iode en application du Plan Particulier d’Intervention (PPI)</t>
+  </si>
+  <si>
+    <t>1688</t>
+  </si>
+  <si>
+    <t>Remise du kit de dépistage du cancer colorectal</t>
   </si>
   <si>
     <t/>
@@ -7951,7 +8197,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1267"/>
+  <dimension ref="A1:B1308"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -18083,15 +18329,343 @@
         <v>2556</v>
       </c>
       <c r="B1266" t="s" s="2">
-        <v>2556</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="s" s="2">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="B1267" t="s" s="2">
-        <v>2558</v>
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="s" s="2">
+        <v>2560</v>
+      </c>
+      <c r="B1268" t="s" s="2">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="s" s="2">
+        <v>2562</v>
+      </c>
+      <c r="B1269" t="s" s="2">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="s" s="2">
+        <v>2564</v>
+      </c>
+      <c r="B1270" t="s" s="2">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="s" s="2">
+        <v>2566</v>
+      </c>
+      <c r="B1271" t="s" s="2">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="s" s="2">
+        <v>2568</v>
+      </c>
+      <c r="B1272" t="s" s="2">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="s" s="2">
+        <v>2570</v>
+      </c>
+      <c r="B1273" t="s" s="2">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="s" s="2">
+        <v>2572</v>
+      </c>
+      <c r="B1274" t="s" s="2">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="s" s="2">
+        <v>2574</v>
+      </c>
+      <c r="B1275" t="s" s="2">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="s" s="2">
+        <v>2576</v>
+      </c>
+      <c r="B1276" t="s" s="2">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="s" s="2">
+        <v>2578</v>
+      </c>
+      <c r="B1277" t="s" s="2">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="s" s="2">
+        <v>2580</v>
+      </c>
+      <c r="B1278" t="s" s="2">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="s" s="2">
+        <v>2582</v>
+      </c>
+      <c r="B1279" t="s" s="2">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="s" s="2">
+        <v>2584</v>
+      </c>
+      <c r="B1280" t="s" s="2">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="s" s="2">
+        <v>2586</v>
+      </c>
+      <c r="B1281" t="s" s="2">
+        <v>2587</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="s" s="2">
+        <v>2588</v>
+      </c>
+      <c r="B1282" t="s" s="2">
+        <v>2589</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="s" s="2">
+        <v>2590</v>
+      </c>
+      <c r="B1283" t="s" s="2">
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="s" s="2">
+        <v>2592</v>
+      </c>
+      <c r="B1284" t="s" s="2">
+        <v>2593</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="s" s="2">
+        <v>2594</v>
+      </c>
+      <c r="B1285" t="s" s="2">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="s" s="2">
+        <v>2596</v>
+      </c>
+      <c r="B1286" t="s" s="2">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="s" s="2">
+        <v>2598</v>
+      </c>
+      <c r="B1287" t="s" s="2">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="s" s="2">
+        <v>2600</v>
+      </c>
+      <c r="B1288" t="s" s="2">
+        <v>2601</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="s" s="2">
+        <v>2602</v>
+      </c>
+      <c r="B1289" t="s" s="2">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="s" s="2">
+        <v>2604</v>
+      </c>
+      <c r="B1290" t="s" s="2">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="s" s="2">
+        <v>2606</v>
+      </c>
+      <c r="B1291" t="s" s="2">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="s" s="2">
+        <v>2608</v>
+      </c>
+      <c r="B1292" t="s" s="2">
+        <v>2609</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="s" s="2">
+        <v>2610</v>
+      </c>
+      <c r="B1293" t="s" s="2">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="s" s="2">
+        <v>2612</v>
+      </c>
+      <c r="B1294" t="s" s="2">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="s" s="2">
+        <v>2614</v>
+      </c>
+      <c r="B1295" t="s" s="2">
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="s" s="2">
+        <v>2616</v>
+      </c>
+      <c r="B1296" t="s" s="2">
+        <v>2617</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="s" s="2">
+        <v>2618</v>
+      </c>
+      <c r="B1297" t="s" s="2">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="s" s="2">
+        <v>2620</v>
+      </c>
+      <c r="B1298" t="s" s="2">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="s" s="2">
+        <v>2622</v>
+      </c>
+      <c r="B1299" t="s" s="2">
+        <v>2623</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="s" s="2">
+        <v>2624</v>
+      </c>
+      <c r="B1300" t="s" s="2">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="s" s="2">
+        <v>2626</v>
+      </c>
+      <c r="B1301" t="s" s="2">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="s" s="2">
+        <v>2628</v>
+      </c>
+      <c r="B1302" t="s" s="2">
+        <v>2629</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="s" s="2">
+        <v>2630</v>
+      </c>
+      <c r="B1303" t="s" s="2">
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="s" s="2">
+        <v>2632</v>
+      </c>
+      <c r="B1304" t="s" s="2">
+        <v>2633</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="s" s="2">
+        <v>2634</v>
+      </c>
+      <c r="B1305" t="s" s="2">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="s" s="2">
+        <v>2636</v>
+      </c>
+      <c r="B1306" t="s" s="2">
+        <v>2637</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="s" s="2">
+        <v>2638</v>
+      </c>
+      <c r="B1307" t="s" s="2">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="s" s="2">
+        <v>2639</v>
+      </c>
+      <c r="B1308" t="s" s="2">
+        <v>2640</v>
       </c>
     </row>
   </sheetData>
